--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:44</t>
+    <t xml:space="preserve">2026-09-24 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -576,13 +576,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="3">
@@ -599,10 +599,10 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.74</v>
@@ -622,10 +622,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.79</v>
@@ -645,13 +645,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +668,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.36</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="9">
@@ -737,13 +737,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -760,13 +760,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="11">
@@ -783,13 +783,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="12">
@@ -806,7 +806,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.14</v>
@@ -829,13 +829,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="14">
@@ -852,13 +852,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="15">
@@ -875,13 +875,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -898,13 +898,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-0.26</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -921,13 +921,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="18">
@@ -950,7 +950,7 @@
         <v>-0.23</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="19">
@@ -967,13 +967,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="20">
@@ -990,13 +990,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="21">
@@ -1013,13 +1013,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -1059,13 +1059,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.16</v>
+        <v>-0.08</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>-0.4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="25">
@@ -1108,10 +1108,10 @@
         <v>-0.71</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="26">
@@ -1131,10 +1131,10 @@
         <v>-0.39</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="27">
@@ -1151,10 +1151,10 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0.09</v>
@@ -1174,13 +1174,13 @@
         <v>10</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="29">
@@ -1203,7 +1203,7 @@
         <v>0.12</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="30">
@@ -1223,10 +1223,10 @@
         <v>-0.07</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31">
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="33">
@@ -1289,7 +1289,7 @@
         <v>16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>0.02</v>
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="35">
@@ -1335,13 +1335,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="36">
@@ -1358,13 +1358,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="37">
@@ -1381,13 +1381,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="38">
@@ -1404,7 +1404,7 @@
         <v>16</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>-0.32</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="42">
@@ -1496,7 +1496,7 @@
         <v>30</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>-0.24</v>
@@ -1519,13 +1519,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>0.31</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0.36</v>
       </c>
     </row>
     <row r="44">
@@ -1542,13 +1542,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="45">
@@ -1565,13 +1565,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.42</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="46">
@@ -2025,13 +2025,13 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="66">
@@ -2048,13 +2048,13 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="67">
@@ -2071,13 +2071,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.47</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:34</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_o_higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
